--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -1858,7 +1858,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15214,16 +15214,16 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O85" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.3643383456729046</v>
+        <v>0.3624003757491125</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15376,10 +15376,10 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O86" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17686,16 +17686,16 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O99" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17848,10 +17848,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O100" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -18478,16 +18478,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="O103" t="n">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.7778789479122045</v>
+        <v>0.9256324910910589</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342354</v>
+        <v>342398</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -1858,7 +1858,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15214,16 +15214,16 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O85" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.3624003757491125</v>
+        <v>0.3643383456729046</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15376,10 +15376,10 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O86" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17290,16 +17290,16 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -17452,10 +17452,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -17686,16 +17686,16 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O99" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.06976691725651366</v>
+        <v>0.08527067664685002</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17848,10 +17848,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O100" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -18478,16 +18478,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="O103" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.9256324910910589</v>
+        <v>1.042966187144855</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342398</v>
+        <v>342436</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -16006,16 +16006,16 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="O89" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>4.397840755794139</v>
+        <v>4.389149370901265</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17686,16 +17686,16 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O99" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.08527067664685002</v>
+        <v>0.09883646611339433</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17848,10 +17848,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O100" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -18478,16 +18478,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="O103" t="n">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>1.042966187144855</v>
+        <v>1.268942194359574</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18556,6 +18556,154 @@
       <c r="BC103" t="inlineStr">
         <is>
           <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>161</v>
+      </c>
+      <c r="O104" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.1315061536180884</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18592,7 +18740,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -18675,7 +18823,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -18685,7 +18833,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -18737,7 +18885,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342436</v>
+        <v>342654</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -927,9 +927,6 @@
       <c r="O3" t="n">
         <v>105</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>1.16565668990357</v>
       </c>
@@ -1223,9 +1220,6 @@
       <c r="O5" t="n">
         <v>20</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.3557618341728275</v>
       </c>
@@ -1619,9 +1613,6 @@
       <c r="O7" t="n">
         <v>169</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.3275169171208557</v>
       </c>
@@ -1868,7 +1859,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2015,9 +2006,6 @@
       <c r="O9" t="n">
         <v>14</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.2476566156113709</v>
       </c>
@@ -3165,9 +3153,6 @@
       <c r="O16" t="n">
         <v>105</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>1.16565668990357</v>
       </c>
@@ -3461,9 +3446,6 @@
       <c r="O18" t="n">
         <v>25</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.4447022927160344</v>
       </c>
@@ -3857,9 +3839,6 @@
       <c r="O20" t="n">
         <v>138</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2674398494833023</v>
       </c>
@@ -4106,7 +4085,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4253,9 +4232,6 @@
       <c r="O22" t="n">
         <v>20</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.3537951651591013</v>
       </c>
@@ -5403,9 +5379,6 @@
       <c r="O29" t="n">
         <v>108</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>1.198961166757958</v>
       </c>
@@ -5699,9 +5672,6 @@
       <c r="O31" t="n">
         <v>24</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.426914201007393</v>
       </c>
@@ -6095,9 +6065,6 @@
       <c r="O33" t="n">
         <v>197</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.3817800749870331</v>
       </c>
@@ -6344,7 +6311,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -6491,9 +6458,6 @@
       <c r="O35" t="n">
         <v>15</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.2653463738693259</v>
       </c>
@@ -7479,9 +7443,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7641,9 +7602,6 @@
       <c r="O42" t="n">
         <v>89</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.9880328133468356</v>
       </c>
@@ -7937,9 +7895,6 @@
       <c r="O44" t="n">
         <v>23</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.4091261092987516</v>
       </c>
@@ -8333,9 +8288,6 @@
       <c r="O46" t="n">
         <v>183</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.3546484960539444</v>
       </c>
@@ -8582,7 +8534,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -8729,9 +8681,6 @@
       <c r="O48" t="n">
         <v>15</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.2653463738693259</v>
       </c>
@@ -9717,9 +9666,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10027,9 +9973,6 @@
       <c r="O56" t="n">
         <v>28</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.4980665678419585</v>
       </c>
@@ -10423,9 +10366,6 @@
       <c r="O58" t="n">
         <v>157</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.3042612780353512</v>
       </c>
@@ -10672,7 +10612,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -10819,9 +10759,6 @@
       <c r="O60" t="n">
         <v>16</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.283036132127281</v>
       </c>
@@ -11955,9 +11892,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12499,9 +12433,6 @@
       <c r="O70" t="n">
         <v>20</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.3557618341728275</v>
       </c>
@@ -12895,9 +12826,6 @@
       <c r="O72" t="n">
         <v>193</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.3740281952918649</v>
       </c>
@@ -13144,7 +13072,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -13291,9 +13219,6 @@
       <c r="O74" t="n">
         <v>18</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.3184156486431911</v>
       </c>
@@ -13687,9 +13612,6 @@
       <c r="O76" t="n">
         <v>987</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>4.289198444633216</v>
       </c>
@@ -13835,9 +13757,6 @@
       <c r="O77" t="n">
         <v>165</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1347733872483514</v>
       </c>
@@ -13983,9 +13902,6 @@
       <c r="O78" t="n">
         <v>209</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.1707129571812452</v>
       </c>
@@ -14131,9 +14047,6 @@
       <c r="O79" t="n">
         <v>170</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.1388574292861803</v>
       </c>
@@ -14279,9 +14192,6 @@
       <c r="O80" t="n">
         <v>167</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.136407004063483</v>
       </c>
@@ -14427,9 +14337,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14823,9 +14730,6 @@
       <c r="O83" t="n">
         <v>13</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.2312451922123379</v>
       </c>
@@ -15214,16 +15118,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O85" t="n">
-        <v>188</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="R85" t="n">
-        <v>0.3643383456729046</v>
+        <v>0.3662763155966967</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15376,10 +15277,10 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O86" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -15468,7 +15369,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -15610,16 +15511,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O87" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R87" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15772,10 +15670,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -16011,9 +15909,6 @@
       <c r="O89" t="n">
         <v>1010</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>4.389149370901265</v>
       </c>
@@ -16159,9 +16054,6 @@
       <c r="O90" t="n">
         <v>172</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.1404910461013118</v>
       </c>
@@ -16307,9 +16199,6 @@
       <c r="O91" t="n">
         <v>183</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.1494759385845352</v>
       </c>
@@ -16455,9 +16344,6 @@
       <c r="O92" t="n">
         <v>163</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.1331397704332199</v>
       </c>
@@ -16603,9 +16489,6 @@
       <c r="O93" t="n">
         <v>173</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.1413078545088776</v>
       </c>
@@ -16751,9 +16634,6 @@
       <c r="O94" t="n">
         <v>129</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.1053682845759838</v>
       </c>
@@ -16899,9 +16779,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17290,16 +17167,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O97" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -17452,10 +17326,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -17686,16 +17560,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O99" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R99" t="n">
-        <v>0.09883646611339433</v>
+        <v>0.1027124059609784</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17848,10 +17719,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O100" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -17940,7 +17811,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -18082,16 +17953,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -18244,10 +18112,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -18478,16 +18346,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="O103" t="n">
-        <v>292</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="R103" t="n">
-        <v>1.268942194359574</v>
+        <v>1.408004352645554</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18630,9 +18495,6 @@
       </c>
       <c r="O104" t="n">
         <v>161</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0.1315061536180884</v>
@@ -18885,7 +18747,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342654</v>
+        <v>342693</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -17560,13 +17560,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="O99" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="R99" t="n">
-        <v>0.1027124059609784</v>
+        <v>0.1220921051988989</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17719,10 +17719,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="O100" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -18346,13 +18346,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="O103" t="n">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="R103" t="n">
-        <v>1.408004352645554</v>
+        <v>1.642671744753147</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342693</v>
+        <v>342757</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -18346,13 +18346,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="O103" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="R103" t="n">
-        <v>1.642671744753147</v>
+        <v>1.660054514538895</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342757</v>
+        <v>342761</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -18346,13 +18346,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="O103" t="n">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="R103" t="n">
-        <v>1.660054514538895</v>
+        <v>1.838227904842807</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342761</v>
+        <v>342802</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -17560,13 +17560,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="O99" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="R99" t="n">
-        <v>0.1220921051988989</v>
+        <v>0.1453477442844034</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17719,10 +17719,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="O100" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -18564,6 +18564,151 @@
         </is>
       </c>
       <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>152</v>
+      </c>
+      <c r="O105" t="n">
+        <v>152</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.1241548779499965</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18602,7 +18747,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18830,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -18695,7 +18840,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -18747,7 +18892,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342802</v>
+        <v>342966</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -12138,7 +12138,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -14686,12 +14686,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -14725,95 +14725,84 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>13</v>
+        <v>58058</v>
       </c>
       <c r="O83" t="n">
-        <v>13</v>
+        <v>58058</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>2</v>
       </c>
       <c r="R83" t="n">
-        <v>0.2312451922123379</v>
+        <v>4.109096262295497</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14829,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -14889,98 +14878,23 @@
       <c r="O84" t="n">
         <v>13</v>
       </c>
+      <c r="R84" t="n">
+        <v>0.2312451922123379</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG84" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN84" t="b">
-        <v>1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -15074,17 +14988,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15118,22 +15032,39 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="O85" t="n">
-        <v>189</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0.3662763155966967</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -15141,6 +15072,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -15153,12 +15142,12 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT85" t="n">
@@ -15166,47 +15155,47 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15222,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -15282,98 +15271,23 @@
       <c r="O86" t="n">
         <v>189</v>
       </c>
+      <c r="R86" t="n">
+        <v>0.3662763155966967</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>매독</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN86" t="b">
-        <v>1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -15467,17 +15381,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15511,22 +15425,39 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>9</v>
+        <v>189</v>
       </c>
       <c r="O87" t="n">
-        <v>9</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0.1592078243215956</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>189</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>매독</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -15534,6 +15465,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -15551,7 +15540,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -15564,42 +15553,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15626,7 +15615,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -15675,98 +15664,23 @@
       <c r="O88" t="n">
         <v>9</v>
       </c>
+      <c r="R88" t="n">
+        <v>0.1592078243215956</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>SER_NO_FHI_903_MONTHLY</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Syfilis</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN88" t="b">
-        <v>1</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -15860,17 +15774,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -15904,81 +15818,170 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1010</v>
+        <v>9</v>
       </c>
       <c r="O89" t="n">
-        <v>1010</v>
-      </c>
-      <c r="R89" t="n">
-        <v>4.389149370901265</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Syfilis</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16010,12 +16013,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16040,7 +16043,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -16049,13 +16052,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>172</v>
+        <v>1010</v>
       </c>
       <c r="O90" t="n">
-        <v>172</v>
+        <v>1010</v>
       </c>
       <c r="R90" t="n">
-        <v>0.1404910461013118</v>
+        <v>4.389149370901265</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -16088,42 +16091,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16188,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -16194,13 +16197,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="O91" t="n">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="R91" t="n">
-        <v>0.1494759385845352</v>
+        <v>0.1404910461013118</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -16330,7 +16333,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -16339,13 +16342,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="O92" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="R92" t="n">
-        <v>0.1331397704332199</v>
+        <v>0.1494759385845352</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16475,7 +16478,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -16484,13 +16487,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="O93" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="R93" t="n">
-        <v>0.1413078545088776</v>
+        <v>0.1331397704332199</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -16620,7 +16623,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -16629,13 +16632,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="O94" t="n">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="R94" t="n">
-        <v>0.1053682845759838</v>
+        <v>0.1413078545088776</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -16735,12 +16738,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16765,104 +16768,90 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N95" t="n">
+        <v>129</v>
+      </c>
+      <c r="O95" t="n">
+        <v>129</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.1053682845759838</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
         <v>0</v>
       </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP95" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AT95" t="n">
-        <v>1</v>
-      </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16878,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16938,98 +16927,23 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN96" t="b">
-        <v>1</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -17123,17 +17037,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17167,22 +17081,39 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>4</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0.07115236683456549</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -17190,9 +17121,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
@@ -17202,12 +17191,12 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -17215,47 +17204,47 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17282,7 +17271,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -17331,98 +17320,23 @@
       <c r="O98" t="n">
         <v>4</v>
       </c>
+      <c r="R98" t="n">
+        <v>0.07115236683456549</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -17516,17 +17430,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17560,22 +17474,39 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
-        <v>75</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.1453477442844034</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -17583,6 +17514,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17595,12 +17584,12 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -17608,47 +17597,47 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17664,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -17724,98 +17713,23 @@
       <c r="O100" t="n">
         <v>75</v>
       </c>
+      <c r="R100" t="n">
+        <v>0.1453477442844034</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>매독</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -17909,17 +17823,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -17953,22 +17867,39 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.07075903303182025</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>75</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>매독</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -17976,6 +17907,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17993,7 +17982,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -18006,42 +17995,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18068,7 +18057,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -18117,98 +18106,23 @@
       <c r="O102" t="n">
         <v>4</v>
       </c>
+      <c r="R102" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_903_MONTHLY</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Syfilis</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN102" t="b">
-        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -18302,17 +18216,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18346,81 +18260,170 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>423</v>
+        <v>4</v>
       </c>
       <c r="O103" t="n">
-        <v>423</v>
-      </c>
-      <c r="R103" t="n">
-        <v>1.838227904842807</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Syfilis</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18452,12 +18455,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18482,7 +18485,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -18491,13 +18494,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>161</v>
+        <v>423</v>
       </c>
       <c r="O104" t="n">
-        <v>161</v>
+        <v>423</v>
       </c>
       <c r="R104" t="n">
-        <v>0.1315061536180884</v>
+        <v>1.838227904842807</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -18530,42 +18533,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18627,7 +18630,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -18636,13 +18639,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="O105" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="R105" t="n">
-        <v>0.1241548779499965</v>
+        <v>0.1315061536180884</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -18709,6 +18712,151 @@
         </is>
       </c>
       <c r="BC105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>152</v>
+      </c>
+      <c r="O106" t="n">
+        <v>152</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.1241548779499965</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18830,7 +18978,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -18840,7 +18988,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
@@ -18892,7 +19040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342966</v>
+        <v>401024</v>
       </c>
     </row>
     <row r="16">
@@ -18902,7 +19050,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -18101,13 +18101,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O102" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R102" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -18260,10 +18260,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O103" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401024</v>
+        <v>401027</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -15659,13 +15659,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R88" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -17315,13 +17315,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O98" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R98" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O99" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -17708,13 +17708,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="O100" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="R100" t="n">
-        <v>0.1453477442844034</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="O101" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -18101,13 +18101,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O102" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R102" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -18260,10 +18260,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O103" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -18857,6 +18857,151 @@
         </is>
       </c>
       <c r="BC106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>105</v>
+      </c>
+      <c r="O107" t="n">
+        <v>105</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.08576488279440546</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18895,7 +19040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18978,7 +19123,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -18988,7 +19133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -19040,7 +19185,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401027</v>
+        <v>401190</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -17708,13 +17708,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="O100" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="R100" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2558120299405501</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="O101" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401190</v>
+        <v>401197</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17315,13 +17315,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R98" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401197</v>
+        <v>401198</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -17708,13 +17708,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="O100" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="R100" t="n">
-        <v>0.2558120299405501</v>
+        <v>0.2771296991022626</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="O101" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401198</v>
+        <v>401209</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -43723,13 +43723,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O241" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R241" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -43887,10 +43887,10 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O242" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
@@ -44126,13 +44126,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O243" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R243" t="n">
-        <v>0.3178270675018955</v>
+        <v>0.3255789471970637</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -44285,10 +44285,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O244" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -46443,13 +46443,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O256" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R256" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -46602,10 +46602,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O257" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>585438</v>
+        <v>585451</v>
       </c>
     </row>
     <row r="16">
